--- a/sheet/bossspellcard.xlsx
+++ b/sheet/bossspellcard.xlsx
@@ -609,22 +609,22 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1 阶段符卡：66%~100% 血时，花符[弹幕花环]。大妖精悬停不动，每有一名被锁定的玩家（最多 5 名），就在它身后 6 格处生成一个由 48 颗弹组成的竖直圆环，圆环平面垂直于「BOSS → 该玩家」的方向，并在生成那一 tick 锁定，此后 BOSS 转向不影响已生成的环。48 颗在同一 tick 全部生成（不逐颗错开），生成后先在原地停住；停满 3 秒后，每颗弹重新瞄准它所属的那名玩家，以 12 格/秒射出——每个环只追自己的目标。因不同玩家而生成的环在同一 tick 同时出现。出生后前 3 秒不判伤，起飞的瞬间才开始生效。符卡循环 12 秒：前 6 秒锁位悬停，后 6 秒恢复随机游走，整个循环走完后重复。</t>
+          <t>1 阶段符卡：66%~100% 血时，花符[弹幕花环]。大妖精悬停不动，每有一名被锁定的玩家（最多 5 名），就在它身后 6 格处生成一个由 48 颗弹组成的竖直圆环；圆环平面垂直于「BOSS → 该玩家」的方向，并在本颗出现时所在的组帧里保持共圆。48 颗不是同时出现，而是每隔 0.1 秒出现 1 颗，4.8 秒后全部出现；全部出现后先等 1 秒，再从先到后每隔 0.1 秒射出 1 颗。每一颗在射出瞬间重新瞄准它所属玩家的当前位置，以 12 格/秒飞出——先出现的先射，后出现的后射，且每颗都追当前站位。出现期间只可见、不判伤；起飞的那一瞬间才开始生效。不同玩家的环各自独立。符卡循环 12 秒：前 6 秒锁位，后 6 秒恢复游走，整个循环走完后重复。</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>轨「花环」×1：DISC_RING 侧挂圆盘，48 颗/次，半径 4 格，圆心在 BOSS 身后 6 格；AIMED（按人复制，最多 5 人 = 240 颗/轮）；球弹；运动 = 定时重瞄（RECLAIM），无需编队帧。</t>
+          <t>轨「花环」×1：AIMED（按人复制，最多 5 人），每人一个组；组帧在进入符卡时锁定，圆心在 BOSS 身后 6 格、半径 4 格，保证 48 颗严格共圆。组内用一个不可见载体沿组帧 Z 轴扫描：每 2 tick 留一颗出现弹（寿命 116 tick，正好到该位的发射时刻）和一颗攻击弹（AIM_LOCAL，出生即按当时目标位置定向）；球弹。</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>每环 48 颗｜环半径 4 格｜圆心后移 6 格｜直径 0.7 格｜出生速率 0.6 格/tick(12 格/秒)，1 tick 内减速到 0｜静止 60 tick(3s) 后重瞄所属玩家，以 0.6 格/tick(12 格/秒)射出｜无害窗口 60 tick(3s)｜寿命 400 tick(20s)｜伤害倍率 1.0</t>
+          <t>每环 48 颗｜环半径 4 格｜圆心后移 6 格｜直径 0.7 格｜出现间隔 2 tick(0.1s)，4.8 秒全部出现｜全部出现后等 20 tick(1s)｜射出间隔 2 tick(0.1s)，4.8 秒射完｜射出速度 0.6 格/tick(12 格/秒)｜出现弹寿命 116 tick(5.8s)，攻击弹出生即判伤、寿命 400 tick(20s)｜伤害倍率 1.0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>240 tick = 12 秒（6 秒锁位放环 + 6 秒游走）。血量跨阈值时切卡挂起，等本循环走完才切。</t>
+          <t>240 tick = 12 秒（4.8 秒出现 + 1 秒等待 + 4.8 秒射出 + 1.4 秒间歇）。</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>BossCards#ringCard()；BigFairyEntity#movementLocked()；lang spellcard.gensokyou.big_fairy.1</t>
+          <t>BigFairyPrograms#ring()；lang spellcard.gensokyou.big_fairy.1</t>
         </is>
       </c>
     </row>
@@ -1019,18 +1019,18 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2 阶段符卡：75%~50% 血时，瘴符「瘴气充溢」。中央一团以山女为编队中心的确定性螺旋：按阿基米德螺线在面向玩家的竖直平面内排布 20 颗弹，内半径 3 格、外半径 8 格、绕 1 圈，初速沿平面法线以 3.6 格/秒朝玩家推出。整团挂编队呼吸，出生时是 0.6 倍的收拢态，2 秒后完全张开到 1.4 倍（内 1.8 / 外 4.8 → 内 4.2 / 外 11.2 格），再 2 秒收回，以此 4 秒为周期往返；螺旋不自转，只整体缩放。每 3 秒重发一轮，每次相位推进 9°，新的一圈接在旧的一圈外沿上。第二轨「毒雾」每 1.5 秒在朝玩家的半球内随机散射 7 颗缓速弹（2.4 格/秒），飘向玩家所在的方向。符卡循环 13 秒；前 6.5 秒锁位，后 6.5 秒游走。</t>
+          <t>2 阶段符卡：75%~50% 血时，瘴符「瘴气充溢」。以山女当前位置为编队中心，对每名被锁定的玩家（最多 5 名）各生成一份精确朝向该玩家的确定性螺旋：按阿基米德螺线在「山女 → 该玩家」的竖直平面内排布 20 颗弹，内半径 3 格、外半径 8 格、绕 1 圈，初速沿平面法线以 7.2 格/秒朝该玩家推出。整团挂编队呼吸，出生时 0.6 倍收拢，2 秒后张开到 1.4 倍，再 2 秒收回，以此 4 秒为周期往返；螺旋不自转，只整体缩放。每 3 秒重发一轮，每次按当时位置与目标方向重建组，因此上一轮生成的弹保持自己的快照、新一轮面向玩家当前站位。第二轨「毒雾」每 1.5 秒在朝玩家的半球内随机散射 7 颗缓速弹（2.4 格/秒）。符卡循环 13 秒；前 6.5 秒锁位，后 6.5 秒游走。</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>轨「瘴涡」：SPIRAL 螺旋 20 颗（1 圈，r 3 → 8 格），每 60 tick 一轮，相位步进 9°；编队 = 呼吸（基准 1.0 / 幅度 0.4 / 周期 80 tick）；穿墙球弹；SELF_AXIS。
-轨「毒雾」：CONE_RANDOM（总张角 180°）7 颗，每 30 tick 一次，相位步进 41°；穿墙球弹；SELF_AXIS。</t>
+          <t>轨「瘴涡」：每 60 tick、每名被锁定玩家各建一个 AIMED 组；SPIRAL 20 颗（1 圈，r 3 → 8 格），相位 0；编队 = 呼吸（基准 1.0 / 幅度 0.4 / 周期 80 tick）；穿墙球弹；沿法线推进 0.36 格/tick。多人 = 每人一份，不是每人五份。
+轨「毒雾」：CONE_RANDOM（总张角 180°）7 颗，每 30 tick 一次；穿墙球弹；SELF_AXIS。</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>瘴涡 周期 60 tick(3s)、相位 9°/轮、20 颗、圈数 1、内径 3 / 外径 8 格、直径 0.55 格、弹速 0.18 格/tick(3.6 格/秒)、编队呼吸 0.6↔1.4 倍 / 周期 80 tick(4s)｜毒雾 周期 30 tick(1.5s)、相位 41°、7 颗、总张角 180°、直径 0.5 格、弹速 0.12 格/tick(2.4 格/秒)｜寿命 均 400 tick(20s)｜伤害倍率 均 1.0</t>
+          <t>瘴涡 周期 60 tick(3s)、20 颗/人/轮、圈数 1、内径 3 / 外径 8 格、直径 0.55 格、弹速 0.36 格/tick(7.2 格/秒)、编队呼吸 0.6→1.4 倍 / 周期 80 tick(4s)｜毒雾 周期 30 tick(1.5s)、7 颗、总张角 180°、直径 0.5 格、弹速 0.12 格/tick(2.4 格/秒)｜寿命 均 400 tick(20s)｜伤害倍率 均 1.0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>BossCards#miasmaCard()；lang spellcard.gensokyou.yamame.2</t>
+          <t>YamamePrograms#miasma()；lang spellcard.gensokyou.yamame.2</t>
         </is>
       </c>
     </row>
@@ -1145,21 +1145,20 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4 阶段符卡：25%~0% 血时，瘴气「原因不明之热病」。三重瘴气螺旋同步展开：中央大螺旋每 2.5 秒重发一轮（14 颗，内径 3 / 外径 9 格，绕 1 圈，4 格/秒，编队呼吸 0.55↔1.45 倍 / 3.5 秒周期）；左右两个小螺旋分别挂在山女水平左、右手侧 6 格处，各每 2.5 秒重发一轮（各 6 颗，内径 1.5 / 外径 4 格，4.4 格/秒，编队呼吸 0.6↔1.4 倍 / 3 秒周期），一正一反旋向、颜色不同，读起来是一对。第四轨「毒雾」每 1.3 秒在朝玩家的半球内随机散射 7 颗缓速弹（2.4 格/秒），把威胁铺向玩家所在的方向，逼其不能一味绕场。本卡的难度来自安全区变化速度与三组图案的空间关系，而不是弹数——四条轨的伤害一律上抬到标准伤害的 1.25 倍。符卡循环 13 秒；前 6.5 秒锁位，后 6.5 秒游走。</t>
+          <t>4 阶段符卡：25%~0% 血时，瘴气「原因不明之热病」。对每名被锁定的玩家各生成一份三重瘴气螺旋：中央大螺旋每 2.5 秒重发一轮（14 颗，内径 3 / 外径 9 格，绕 1 圈，8 格/秒，编队呼吸 0.55↔1.45 倍 / 3.5 秒周期）；左右两个小螺旋分别挂在该玩家方向的左右手侧 6 格处（各 6 颗，内径 1.5 / 外径 4 格，8.8 格/秒，编队呼吸 0.6↔1.4 倍 / 3 秒周期），一正一反旋向、颜色不同。每轮都按山女当时位置与目标方向重建组，已生成的弹保持自己的快照。第四轨「毒雾」每 1.3 秒朝玩家方向散射 7 颗缓速弹。四条轨伤害一律为标准伤害的 1.25 倍。符卡循环 13 秒；前 6.5 秒锁位，后 6.5 秒游走。</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>轨「热病中心」：SPIRAL 14 颗（1 圈，r 3 → 9 格），周期 50 tick，相位步进 11°，编队呼吸 幅度 0.45 / 周期 70 tick。
-轨「热病左」：SPIRAL 6 颗（1 圈，r 1.5 → 4 格），周期 50 tick，水平右偏移 +6 格（即山女左手侧），编队呼吸 幅度 0.4 / 周期 60 tick。
-轨「热病右」：同「热病左」，但旋向相反、水平右偏移 −6 格。
-轨「毒雾」：CONE_RANDOM（总张角 180°）7 颗，周期 26 tick，相位步进 53°。
-四轨均穿墙球弹、SELF_AXIS（不按人复制）。</t>
+          <t>轨「热病中心」：每 50 tick、每名玩家各建一个 AIMED 组；SPIRAL 14 颗（1 圈，r 3 → 9 格），相位 0；编队呼吸 0.45 / 70 tick；推进 0.40 格/tick。
+轨「热病左 / 右」：从该玩家的中心组各偏移 ±6 格建组；SPIRAL 6 颗（1 圈，r 1.5 → 4 格），一正一反；呼吸 0.4 / 60 tick；推进 0.44 格/tick。
+轨「毒雾」：CONE_RANDOM 7 颗，周期 26 tick。
+四轨均穿墙球弹；多人 = 每人一份三重螺旋。</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>中心 周期 50 tick(2.5s)、相位 11°、14 颗、内 3 / 外 9 格、直径 0.5 格、弹速 0.20 格/tick(4 格/秒)、编队呼吸 0.55↔1.45 倍 / 70 tick(3.5s)｜左右各 周期 50 tick、各 6 颗、内 1.5 / 外 4 格、横向偏移 ±6 格、直径 0.45 格、弹速 0.22 格/tick(4.4 格/秒)、编队呼吸 0.6↔1.4 倍 / 60 tick(3s)、旋向一正一反｜毒雾 周期 26 tick(1.3s)、相位 53°、7 颗、弹速 0.12 格/tick(2.4 格/秒)、直径 0.5 格｜寿命 均 400 tick(20s)｜伤害倍率 四轨均 1.25×</t>
+          <t>中心 周期 50 tick(2.5s)、14 颗/人、内 3 / 外 9 格、直径 0.5、弹速 0.40(8 格/秒)、呼吸 0.55→1.45 / 70 tick｜左右 各 6 颗/人、内 1.5 / 外 4 格、横向偏移 ±6 格、直径 0.45、弹速 0.44(8.8 格/秒)、呼吸 0.6→1.4 / 60 tick、旋向一正一反｜毒雾 周期 26 tick(1.3s)、7 颗、弹速 0.12(2.4 格/秒)｜寿命 均 400 tick(20s)｜伤害倍率 四轨均 1.25×</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1179,7 +1178,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>BossCards#feverCard()；lang spellcard.gensokyou.yamame.4</t>
+          <t>YamamePrograms#fever()；lang spellcard.gensokyou.yamame.4</t>
         </is>
       </c>
     </row>

--- a/sheet/bossspellcard.xlsx
+++ b/sheet/bossspellcard.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大妖精" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="黑谷山女" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="八云蓝残魂" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="大妖精" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="黑谷山女" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="八云蓝残魂" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="露米娅" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'大妖精'!$A$1:$L$5</definedName>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,8 +41,12 @@
       <i val="1"/>
       <color rgb="FF808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,8 +58,13 @@
         <fgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F2433"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -62,11 +72,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00666666"/>
+      </left>
+      <right style="thin">
+        <color rgb="00666666"/>
+      </right>
+      <top style="thin">
+        <color rgb="00666666"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00666666"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -75,6 +99,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -767,7 +797,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -1182,7 +1211,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -2117,4 +2145,466 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>BOSS</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>阶段</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>血量区间</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>符卡名（中）</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>符卡名（英）</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>规则描述</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>弹幕构成（分轨）</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>关键参数</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>符卡循环</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>移动锁 / 演出</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>颜色</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>代码位置</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>露米娅</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>1 阶段</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>75% ~ 100%</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>月符「月光射线」</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Moon Sign: Moonlight Ray</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>无光之夜中唯一一道笔直落下的月光。它不是照明，而是「被看见」的瞬间——光既是她的招式，也是她的破绽。官方出处：东方红魔乡 Stage 1（道中/Boss），系列第一张符卡。意象关键词：唯一的光、直线、揭示。</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>#BFD8FF 月光蓝</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>RumiaPrograms#card1；lang spellcard.gensokyou.rumia.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>露米娅</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2 阶段</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>50% ~ 75%</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>夜符「夜鸟」</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Night Sign: Night Bird</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>夜空中振翅的鸟群。两翼交替拍动，黑暗像羽毛一样一层层落下；没有固定中心，玩家追着「翅膀」的节拍走。官方出处：东方红魔乡 Stage 1 Boss，系列第一张 Boss 符卡。意象关键词：双翼、交替、夜色、群体。</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>#9C7BFF 夜紫</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>RumiaPrograms#card2；lang spellcard.gensokyou.rumia.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>露米娅</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>3 阶段</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>25% ~ 50%</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>暗符「境界线」</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Dark Sign: Demarcation</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>她在光与暗之间划下的一条界线。界内是她的领域，界外是玩家的世界；界线会停驻、收缩、再展开，像一次呼吸。玩家不是要打败黑暗，而是要在界线移动时找到那条还没闭合的缝。官方出处：东方红魔乡 Stage 1 Boss（Hard/Lunatic）。意象关键词：界线、领域、收束/展开。</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>#D0433C 暗红</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>RumiaPrograms#card3；lang spellcard.gensokyou.rumia.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>露米娅</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>4 阶段</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0% ~ 25%</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>暗符「月之暗面」</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Dark Sign: Dark Side of the Moon</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>月亮背向人类的那一面。终符把「看不见的暗」具象成一颗绕行的暗球/一轮被遮住的月：你只看到被照亮的一半，另一半永远在她的掌控里。官方出处：东方红魔乡 Extra（道中 Boss）。意象关键词：月背、暗球、遮蔽、终局。</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>#7A5CFF 终局紫</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>RumiaPrograms#card4；lang spellcard.gensokyou.rumia.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>露米娅</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>T1 最终</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>100% ~ 0%</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>4 张官方卡</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Four Official Spell Cards</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>T1 强度上限，不是 1→2 的进度门。目标战斗时长 240 秒、目标可挨发数 7、移动距离带 7~24 格、悬空高度带 召唤锚点上方 3~8 格、最多锁定 5 名玩家。游戏内表现（分轨/参数/循环/移动锁/演出）由用户设计；本页只记录官方卡名、意象与考据。</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>建议：月光蓝 / 夜紫 / 暗红 / 终局紫</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>BossProgramCards#rumia；BossProgramManifest；RumiaPrograms</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>露米娅</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>考据与命名说明</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>资料截至 2026-10-24</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>四张均为官方卡名</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Sources and Naming</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>官方内容核对以《东方红魔乡》Stage 1 / Extra 为准。月符「ムーンライトレイ」、夜符「ナイトバード」、闇符「ディマーケイション」、闇符「ダークサイドオブザムーン」均为官方卡名；中文名为项目内译名，英文名为常用译名。未选：夜符「ミッドナイトバード」——它是 Night Bird 的 Extra 变体，母题重复，作为变体排除。本页不设计游戏内表现；分轨/参数/循环/移动锁留空或写「待用户设计」。</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>sheet：本页为设计意图，代码当前为最小占位程序</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sheet/bossspellcard.xlsx
+++ b/sheet/bossspellcard.xlsx
@@ -15,9 +15,6 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'大妖精'!$A$1:$L$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'黑谷山女'!$A$1:$L$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'八云蓝残魂'!$A$1:$L$14</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'八云蓝残魂'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'八云蓝残魂'!$A$1:$L$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +41,16 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -64,7 +71,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -86,11 +93,25 @@
         <color rgb="00666666"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -104,6 +125,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1228,922 +1255,1386 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="82" customWidth="1" min="6" max="6"/>
-    <col width="64" customWidth="1" min="7" max="7"/>
-    <col width="64" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="84" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>BOSS</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>阶段</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>血量区间</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>符卡名（中）</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>符卡名（英）</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>规则描述</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>弹幕构成（分轨）</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>关键参数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>符卡循环</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>移动锁 / 演出</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>颜色</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>代码位置</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="300" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="108" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>八云蓝残魂</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>设计定位 / 状态</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>T2 最终 BOSS；中前期</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>八张残式；名称均为拟定</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Eight Remnant Patterns — Proposed</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>设计稿，尚未实现、尚未实机调平衡。魂体只持有八云蓝正主的一部分力量：保留狐火连射、两个式神发射点和简单式弹变化。八张卡是有限能力的递进变奏，不是八项完整绝技。前半场学节奏与穿隙，后半场组合已学规则；允许有二阶最终 BOSS 的持续弹幕强度，但不要求极限擦弹、强制飞行或快速回头找弹。
-正主预留：十二式神完整协奏、天狐公主瞬移显现、Ultimate Buddhist 大小旋转光阵、片面接触的完整散开—停顿—旋转收束—再展开、式神橙、狐狗狸契约移动边界、完整饭纲权现降临。本表终符采用残魂原创主题，不提前使用正主完整终符。</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>八张实际伤害轨道最多两条；两侧同类式神属于一条编排轨。符印只是无伤害的发射提示，不是可攻击召唤物，也不携带独立 AI。第 4 张独占少量激光；第 6 张只做一次转向。</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>默认数值参照现有配置：T2、目标 320 秒、基础挨弹数目标 9；均是配置目标而非实测结论。首版普通弹倍率 1.0，终符 1.1；密度、碰撞与反应时间验证后再校准。</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>每卡 240 tick = 12 秒；时间轴全部显式枚举，20 tick = 1 秒。完整一轮后重复；分阶段攻击互不叠加。</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>正式本地化目前仍称“八云蓝残影”；本页按本次需求称“八云蓝残魂”，不表示已修改实体名称。</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>金 / 狐火青 / 白 / 符纸黄 / 紫；颜色区分轨道，同色不承担冲突语义。</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待实现：BossCards#yakumoRan；YakumoRanEntity；本页不是现行代码说明。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="300" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>100% ~ 0%（T2 最终 BOSS）</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>八云蓝残魂 · 符卡重设计参考</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Remnant Ran — Spell Card Reference</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>旧稿八卡全部退回重做；本页改为重设计参考，不保留旧轨道、数值与时间轴。
+残魂设定（沿用旧稿，待确认）：只持有八云蓝的一部分力量——狐火连射、两个式神发射点、简单式弹变化；完整十二式神协奏、天狐瞬移、卍字光阵、片面接触全展开、式神橙、狐狗狸契约、饭纲权现等正主绝技是否下放，由重设计决定。
+下表先列《东方妖妖梦》Extra 10 张 + Phantasm 中 BOSS 2 张，共 12 张官方卡；8 个槽位如何取舍、每卡的血量区间/循环/轨道/演出，全部留空待设计。</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>主战卡池 12 张；另有文花帖 / 噩梦日记 / 兽王园 8 张非主战卡，见末行备查。</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>官方卡按符卡顺序，不是血量分段；C 列统一 —。</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>每卡循环待设计；旧稿 240 tick / t=220 收束不再自动沿用。</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>每卡移动锁与演出待设计；旧稿锁位规则仅作参考，见共通底线。</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>建议沿用角色色盘：青 #66E8FF / 金 #F2C14E / 白 #F5F0E6 / 黄 #FFE066 / 紫 #9C6BFF。</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>参考：YakumoRanPrograms.java；BossCards#yakumoRan；lang spellcard.gensokyou.yakumo_ran.*</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="124" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>八云蓝残魂</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>共通表演契约</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Extra 第1符</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>式神「仙狐思念」</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Shikigami "Senko Thoughtful Meditation"</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>【意象】仙狐＝长寿、善良之狐；思念＝心念、读心。狐火般的楔形弹从整片战场指向玩家，是“被思念锁定”的具象。
+【原作】蓝向全场撒出大量楔形弹，所有弹道都朝玩家当前位置收束，分三波推进。玩家只需沿一个方向缓慢横移，从楔弹缝隙中穿出；越是大幅闪避，越容易被下一波堵住。初见像全屏弹幕，熟练后是“自机狙楔形栅栏”。
+【出处】东方妖妖梦 Extra 第1符。
+【关键词】全屏楔弹 / 全部自机狙 / 三波 / 缓慢横移 / 初见压迫</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>青 #66E8FF / 金 #F2C14E</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>现行：YakumoRanPrograms#card1；lang .1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="140" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>八云蓝残魂</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Extra 第2符</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>式神「十二神将之宴」</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Shikigami "Banquet of the Twelve General Gods"</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>【意象】十二神将＝守护药师如来的十二武神，也对应十二地支、阴阳道十二天将；十二个魔法阵就是十二个式神。宴＝轮番献艺、十二重协奏。
+【原作】蓝展开十二个魔法阵，每个阵按自己的节奏放出不同弹幕（楔弹、螺旋、45°斜射等），同时蓝本体也不断放自机狙青小弹（约 10° 间隔）。十二阵不是同时全开，而是轮转、分批；中段还有双重红紫楔弹压来。玩家要读“现在是谁在说话”，在阵与阵的间隙里换位。
+【出处】东方妖妖梦 Extra 第2符。
+【关键词】十二魔法阵 / 轮转协奏 / 多弹种 / 自机狙穿插 / 长期战</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>金 #F2C14E / 青 #66E8FF</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>现行：card5；lang .5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="124" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>八云蓝残魂</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Extra 第3符</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>式辉「狐狸妖怪激光」</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Shiki Brilliance "Kitsune-Tanuki Youkai Laser"</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>【意象】狐狸妖怪＝狐与狸、魑魅魍魉；式辉＝式神发出的光。大弹的飞行轨迹本身就是激光的“引线”，光沿狐火走过的路亮起。
+【原作】蓝朝玩家方向发射大弹，大弹沿途向斜下方撒小弹；随后以这条轨迹为轴，放出数道平行激光。激光出现前有细预警线，预警阶段无判定；激光根部可以横向穿过。玩家通常贴近蓝的正面，让大弹垂直落下，再横移让开光束。
+【出处】东方妖妖梦 Extra 第3符。
+【关键词】自机狙大弹 / 轨迹撒弹 / 轨迹轴激光 / 预警线 / 根部可穿 / 贴脸诱导</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>青 #66E8FF / 黄 #FFE066</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>现行：card3；lang .3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="124" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>八云蓝残魂</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Extra 第4符</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>式辉「迷人的四面楚歌」</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Shiki Brilliance "Charming Siege from All Sides"</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>【意象】四面楚歌＝被包围、孤立无援；Charming＝魅惑。狐的狩猎会故意追自己的尾巴、做奇怪动作，让猎物看花眼后走进攻击范围。
+【原作】蓝色针弹在场上织出不断变化的“道路”，红色大玉沿奇异、非直线的轨迹逼近；大玉白色外圈没有判定，真正危险的是内核。道路会随时间被大玉逐步堵死，玩家要在针弹缝隙里找还没闭合的通道。弹道规律难读，是 Extra 最容易被“看花眼”的卡。
+【出处】东方妖妖梦 Extra 第4符。
+【关键词】针弹道路 / 红大玉奇异轨迹 / 白边无判定 / 通道收束 / 魅惑</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>青 #66E8FF / 金 #F2C14E</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>现行：card4；lang .4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="124" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>八云蓝残魂</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Extra 第5符</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>式辉「天狐公主 -Illusion-」</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Shiki Brilliance "Princess Tenko -Illusion-"</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>【意象】天狐＝最高位、神格化的狐；Princess Tenko＝日本逃脱魔术师引田天功；Illusion＝幻术、瞬间移动逃脱。蓝把“出现—撒弹—消失—在别处再现”做成一场魔术。
+【原作】蓝先出现在画面上方，朝玩家方向放出青大弹、青中弹、青小弹的弹群，并以弹群轴为中心撒 32way 蝶弹×4 连；随后消失，魔法阵移动到玩家当前位置，蓝从阵心现身。出现间隔越来越短，最后几乎追着玩家瞬移。蓝本体只有出现时才有判定。
+【出处】东方妖妖梦 Extra 第5符。
+【关键词】瞬移显现 / 魔法阵锁定玩家 / 32way蝶弹 / 间隔递减 / 逃脱魔术</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>青 #66E8FF / 紫 #9C6BFF</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>现行无对应；lang 未用</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="140" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>八云蓝残魂</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Extra 第6符</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>式弹「Ultimate Buddhist」（最后的佛徒）</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Shiki Shot "Ultimate Buddhist"</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>【意象】卍＝佛胸前的吉祥符号，也是日本地图上的寺院标记；Ultimate Buddhist＝究极佛徒。卍字激光旋转，像参拜，也像寺庙庭院里的集体舞。
+【原作】青相位：青色卍字激光由十字逐渐变成卍，缓慢逆时针旋转，同时撒青小弹；一段时间后青弹变樱点、激光消失。红相位：红色卍字激光高速顺时针旋转，配合 5way 自机狙，玩家要顺着激光旋转方向绕圈；约 1.5 圈后红弹变樱点，回到青相位。青慢逆、红快顺，双相位循环。
+【出处】东方妖妖梦 Extra 第6符。
+【关键词】卍字激光 / 十字→卍 / 青慢逆·红快顺 / 5way自机狙 / 绕圈 / 双相位</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>青 #66E8FF / 金 #F2C14E</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>现行无对应；lang 未用</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="124" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>八云蓝残魂</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Extra 第7符</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>式弹「Unilateral Contact」（片面接触）</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Shiki Shot "Unilateral Contact"</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>【意象】Unilateral＝单方面、片面；Contact＝接触。狐凭是狐灵单方面附身于人，不等对方同意；弹幕也像一场上下左右对称的花火，绽放后整体旋转、再压回来。
+【原作】青相位：上下左右对称的花火型弹幕落下，速度先快后慢；随后 6 发自机狙蝶弹（另有 6×6 追加）追来；接着整片弹幕顺时针旋转，转到另一侧后以直线再次压来。红相位相同，但旋转改为逆时针。弹幕飞出画面后仍会被保存，玩家要预判旋转后的落点。
+【出处】东方妖妖梦 Extra 第7符。
+【关键词】对称花火 / 蝶弹自机狙 / 整体旋转 / 画面外保存 / 青顺·红逆</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>青 #66E8FF / 金 #F2C14E</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>现行：card6；lang .6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="140" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>八云蓝残魂</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Extra 第8符</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>式神「橙」</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Shikigami "Chen"</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>【意象】橙＝蓝的式神（猫又），也是蓝“式神使役”能力的具象；之字形＝猫的跳跃。蓝自己不动，让橙代替她满场跑。
+【原作】橙从魔法阵出发，之字形向下移动，沿途撒红蝶弹；到达下角后之字形向上，改撒青蝶弹。橙本体和移动轨迹都有判定。每次折返时，橙沿 x/y 轴放 28way 弹×2；蓝同时持续放 24way 自机狙粒弹；折返点还会放与玩家垂直方向的 9way×2×2。玩家在画面下方小幅上下左右躲避。
+【出处】东方妖妖梦 Extra 第8符。
+【关键词】橙之字形 / 红·青蝶弹 / 轨迹判定 / 折返28way / 蓝24way自机狙</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>金 #F2C14E / 青 #66E8FF</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>现行无对应；lang 未用</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="124" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>八云蓝残魂</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Extra 第9符</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>「狐狗狸先生的契约」</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>"Kokkuri-san's Contract"</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>【意象】狐狗狸＝碟仙/桌灵转，一种召来狐灵的降灵术；契约＝被拉进无法退出的问答。十二把光剑围成牢笼，就是“契约”的边界。
+【原作】70 秒耐久。十二把光剑围住玩家，形成无法离开的牢笼；蓝在笼外不断放青小弹，弹数随时间只增不减。中段四面八方的弹幕像斜墙一样压来，魔法阵在笼内移动、旋转，玩家要一条一条地穿墙。最后剑阵收拢，斜向大弹以 9° 间隔成对落下，直到时间结束。
+【出处】东方妖妖梦 Extra 第9符。
+【关键词】70秒耐久 / 十二剑牢笼 / 青弹累积 / 四向弹墙 / 收束 / 降灵</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>白 #F5F0E6 / 青 #66E8FF</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>现行无对应；lang 未用</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="140" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>八云蓝残魂</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Extra 第10符</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>幻神「饭纲权现降临」</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Illusion God "Descent of Izuna-Gongen"</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>【意象】饭纲权现＝修验道神格，与荼吉尼天、稻荷神被视为同一尊；管狐＝能装进竹筒的小狐式神；降临＝神佛化身逐层显现。六重弹幕就是权现一层层展开的神德。
+【原作】终符。弹幕随剩余血量逐层增加：白粒状 7×18way → 紫蝶 3×32way → 红大弹 2×14way → 青楔 8×48way → 黄中弹 5×48way → 青中弹 [2,2,4]×48way；剩余 30 秒时强制进入最强形态。所有弹道以蓝和其正下方为轴固定，玩家要在不断被填满的缝隙里找“安全地带”。
+【出处】东方妖妖梦 Extra 终符。
+【关键词】逐层加弹 / 六种弹种 / 固定轴 / 安全地带 / 30秒最强 / 权现降临</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>金 #F2C14E / 白 #F5F0E6 / 紫 #9C6BFF</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>现行：card8；lang .8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="140" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>八云蓝残魂</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Phantasm 中 BOSS 第1符</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>式神「前鬼后鬼的守护」</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Shikigami "Protection of Zenki and Goki"</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>【意象】前鬼/后鬼＝役小角使役的红鬼与青鬼，左右随侍守护；守护＝两鬼从两侧替蓝扫出弹幕。黄/绿双色大弹就是两鬼走过的轨迹。
+【原作】黄大弹从蓝的右侧生成、绿大弹从左侧生成，分别朝玩家方向飞出，并在轨迹上不断撒下同色小弹；两鬼一左一右交替，形成两条会拐向玩家的“守护轨迹”。与橙的「青鬼赤鬼」同源：Extra 侧是固定轨道，Phantasm 侧改为自机狙，逃逸空间更小；时间越久，发射间隔越短。
+【出处】东方妖妖梦 Phantasm 中 BOSS 第1符。
+【关键词】左右双鬼 / 黄·绿大弹 / 轨迹撒弹 / 自机狙 / 交替 / 时间加压</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>金 #F2C14E / 青 #66E8FF</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>现行：card2；lang .2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="124" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>八云蓝残魂</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Phantasm 中 BOSS 第2符</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>式神「凭依荼吉尼天」</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Shikigami "Channeling Dakiniten"</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>【意象】荼吉尼天＝空行母，日本以狐为坐骑，与稻荷、饭纲权现同体；凭依＝神附体。蓝被神拖着走，前进方向撒青鳞弹，反方向撒红鳞弹。
+【原作】蓝开始移动，沿前进方向撒青鳞弹，同时在反方向撒红鳞弹；剩余 41 秒后，每隔一段时间追加 9way 紫丸弹自机狙。玩家通常从 6 点方向逆时针绕到中心，再顺时针/逆时针各绕一圈半，跟着蓝的移动方向改变绕行方向。
+【出处】东方妖妖梦 Phantasm 中 BOSS 第2符。
+【关键词】前进·反向双色鳞弹 / 9way紫弹 / 绕圈 / 凭依 / 时间追加</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>青 #66E8FF / 金 #F2C14E / 紫 #9C6BFF</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>现行无对应；lang 未用</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="76" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>八云蓝残魂</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>T2 最终 / 8 卡槽</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>100% ~ 0%</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>空间、瞄准、判伤与收尾</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Shared Performance Rules</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>【坐标】每个“锁轴”时刻记录 BOSS 眼位 O 与主目标胸口 T（脚位上移 0.9 格）；F 为 O→T 单位向量，R 为水平右，U 为与 F、R 正交的上方向；近竖直时用上一有效 R。P(x,y,z)=O+xR+yU+zF，x/y/z 均为格。锁定后的原点、轴与目标点都是世界快照，不随 BOSS 或玩家继续转动。目标面坐标以 T 为原点，平面垂直 F。
-【公平性】所有威胁从 BOSS 附近可见的前方发射区进入战场；不在目标周围临时造环，不在身后生成近距离直瞄弹。每个发射组提前至少 20 tick 显示无伤害符印；激光提前 30 tick 显示与实际光束一致的线。普通弹实际出生点距任何存活战斗玩家至少 6 格；计入双方碰撞体积后，预警开始至最早接触至少 1 秒。出生不满足条件的整个组本轮取消，符印淡出，不平移到玩家附近补发、不积压到下一拍；BOSS 继续寻找合法战斗位置。
-【走位】目标是让地面玩家也能从水平缺口通过；按实际碰撞净宽检查，不把两颗弹中心距当成净宽。主通路净宽至少 2.5 格；辅助直瞄可以暂时经过通路，但必须留可到达的侧移区。跳跃和飞行提供额外解法，不作为唯一解。障碍物可挡弹；若地形吞掉大量弹，检查发射区和 BOSS 选点，不能靠盲目增弹或穿墙掩盖。</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>【多人】整张场景阵列只一份，共用主目标的轴；个人点名仅卡 1/3/7/8 指定轨按目标复制，最多 5 人，均从 BOSS 一侧发出。目标列表在子轮锁轴时快照；目标死亡/退出后取消该目标余下个人拍，不转给其他人。每条主弹路必须覆盖快照目标附近战斗区，禁止仅朝侧面放射。
-【预算】单拍实际展开实体数 ≤48（含子弹/后续派生），多轨错峰；审查真实出生数，不只看 count。表中普通弹无派生分裂，无隐形伤害；球弹撞方块消解，激光被方块裁剪。</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>球弹直径默认 0.40 格，大玉仅卡 8 用 0.70；激光半径 0.18 格（直径 0.36）。每发出生年龄 120 tick 后消解；特殊卡另列更短寿命。预警符印/虚线不碰撞、不伤害、不计弹数。弹数统计为单人、发射未被地形/安全检查取消时的名义值。</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>每轮 t=220 停止本卡全部判伤并在 10 tick 内淡出本卡残弹和预警；t=230..239 清空重整。常规攻击结束后仍有在途弹，不把“停止生成”误写成无压力。t=240 循环边界重新锁轴。血量跨下一阈值则挂起到边界切卡，先清旧卡；不得跨卡残弹叠加。死亡立即清理全部归属攻击。</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>锁位只固定 BOSS 位置，不追随玩家高度；锁位结束恢复既有通用可达性游走。选点优先距主目标约 14~22 格，属于评分目标，不保证距离、更不直接以远离玩家为位移方向。符印锚定到本轮世界快照。</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>青 #66E8FF：主要狐火；金 #F2C14E：交叉/弧弹；白 #F5F0E6：直瞄或辅助；黄 #FFE066：激光；紫 #9C6BFF：终符副轨。</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>待实现共通支持：轮次锁轴/目标快照、组级安全取消、分阶段清弹与判伤收束、发射源预警、卡内移动锁。不能直接依赖现有相位参数实现。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="140" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>8 张候选卡（从 12 张官方卡中选）</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Eight Slots from Twelve Official Cards</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>T2 强度上限，不是 1→2 的进度门。目标战斗时长 320 秒、目标可挨发数 9；移动距离带、悬空高度带、最多锁定人数等按现有 T2 配置复核。
+游戏内表现（分轨/参数/循环/移动锁/演出）由用户设计；本页只记录官方卡名、意象与原作表现。</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>待用户设计</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>建议：青 / 金 / 白 / 黄 / 紫</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>参考：GensokyouConfig ranBossSeconds=320 / ranBossHits=9（旧值，待复核）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="140" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>八云蓝残魂</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>默认攻击（重做）</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>100% ~ 0%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>—（底噪并入各卡节拍）</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>No Independent Background Fire</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>本次重做取消当前独立计时、全程叠加的 3 发狐火扇。普通攻击的连贯感由各卡的连续小批次承担；需要点名的地方在卡内显式安排。特别是激光穿越、启停弹阵和转向观察期，不再有独立扇形突然堵住预留出口。重整时保留尾部符印/收束光效，不追加有伤害底噪。</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>默认攻击轨：0 条。所有有伤害发射都列于下方八卡，表内弹数即全部攻击，不存在未计入的常驻射击。</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>独立默认发射数 0；原 ranFoxfire* 配置如何迁移在实现时处理，本表不声称已经停用。</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>服从卡内时间轴与 t=220 收束，无独立冷却计时。</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>无额外移动逻辑。</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>待实现：YakumoRanEntity#tickDefaultAttack；现有独立攻击仍在运行。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="260" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>旧稿对照 / 卡池边界</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>旧八卡用了什么、漏了什么</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Old Eight vs Official Twelve</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>旧稿八卡：仙狐思念、前鬼后鬼的守护、狐狸妖怪激光、四面楚歌、十二神将之宴、片面接触、式神大星、饭纲权现降临。
+问题一：漏掉妖妖梦 Extra 的天狐公主 -Illusion-、Ultimate Buddhist、式神「橙」、「狐狗狸先生的契约」四张，也没有用 Phantasm 的凭依荼吉尼天。
+问题二：式神大星不是妖妖梦主战卡，而是《秘封噩梦日记》噩梦周三弹幕梦4 与灵乌路空的合作卡；它是官方卡，但不应占用残魂八卡里的妖妖梦主战卡位。
+重设计前先定卡池边界：只取妖妖梦 Extra/Phantasm 12 张，还是允许跨作品取噩梦日记/文花帖/兽王园。</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>8 个槽位从 12 张主战卡中取舍；是否保留 1 张残魂原创终符，待用户设计。</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>旧稿数值全部作废，不沿用。</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>旧稿 240 tick 循环全部作废。</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>旧稿锁位/收束规则见下方共通底线，待复核。</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>旧稿来源：本页历史版本；现行 lang 键 1–8。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="124" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>八云蓝残魂</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>1 阶段</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>(87.5%, 100%]</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>残式「仙狐思念」</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Remnant Formula: Fox Spirit Thoughts</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>开场教“锁定一次、连续发射、横移解开”。每轮三组，起点 b=0/60/120。b 时 BOSS 附近两枚狐火符印亮起并锁轴；对每名目标分别保存胸口快照 Ti，但同组四拍不重新瞄准。b+20/28/36/44 四拍交替从左、右、左、右符印发射。每拍 9 发排成一个平行推进的 3×3 小方阵，以 6 格/秒沿本拍发射点→Ti 的方向直飞；阵列两轴间距 1.5 格，整束宽高 3 格。
-单束看起来是紧凑的狐火群，四拍又形成连续弹路。玩家看到符印锁定后向同一侧移动数格即可避开本组，不需要持续冲刺。下一组会重新瞄准，不能一直站桩。不能把 9 发分别锁定玩家，不允许飞行中追踪。</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>轨「狐念连射」×1，AIMED 按人复制。左右源位于各目标锁轴的 P(−2,0,0) / P(+2,0,0)。每拍方阵围绕源点、位于垂直该拍飞行方向的平面；3×3 共 9 发、统一方向。3 组×4 拍×9=108 发/人/轮。</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>方阵 3×3｜间距 1.5 格｜弹径 0.40｜速度 0.30 格/tick=6 格/秒｜拍间隔 8 tick｜提示 20 tick｜寿命 120 tick｜倍率 1.0｜单人 108 发/12 秒。相邻拍源不同，各拍方向在组开始时由该源→Ti 算定。</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>240 tick。锁定 0/60/120；发射 20/28/36/44、80/88/96/104、140/148/156/164；最后 56 tick 为在途弹通过与收束，220 全部失效。</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>t=0..164 锁位；165..239 游走。每组符印由暗至亮，四次短闪对应四拍；锁定时有一声提示，发射时轻响。</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>狐火青 #66E8FF；两个符印同色、交替亮灭；无第二种伤害语义。</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>待实现：BossCards#yakumoRan 第 1 卡；lang spellcard.gensokyou.yakumo_ran.1。借鉴官方仙狐思念的节奏自机狙，方阵与时序是残魂改编。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="260" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>其他官方卡（非妖妖梦主战）</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>文花帖 / 噩梦日记 / 兽王园</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Other Official Cards (Non-PCB)</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>文花帖（摄影游戏）：密符「大师的秘传」、行符「八千万块护摩」、超人「飞翔役小角」。
+秘封噩梦日记（合作卡）：地妖符「本我的式神」、地妖符「式神大星」、地妖符「自我的式神」。
+兽王园（格斗/对战）：式神「伏击猎人 橙」、式神「多重伏击猎人」。
+这些是官方卡名，但不是妖妖梦主战弹幕，通常不作为残魂八卡的直接原型；列此避免再次把「式神大星」误判为伪卡或漏记。</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>参考：Touhou Wiki「Ran Yakumo/Spell Cards」总表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="236" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>八云蓝残魂</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>2 阶段</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>(75%, 87.5%]</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>残式「双使交替」</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Remnant Formula: Alternating Servants</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>只用两枚式神符印教错拍穿隙。t=0 锁定 O/F/R/U，左源 P(−4,0,0)，右源 P(+4,0,0)。左侧在 t=20/60/100/140 发射，右侧在 t=40/80/120/160 接上，每拍分别提前 20 tick 亮符印；整轮不重新瞄准。
-每拍是沿 F 推进的一面带门弹幕：3 行×7 列，行高 y=−2/0/+2，列间距 2.5 格；七列原始 x=−7.5..+7.5，每行去掉中央 x=0 的弹，共 18 发。弹幕面中心置于 O 平面，左拍整体横移 −1 格、右拍横移 +1 格；点阵直接在所示面板位置生成，符印发光轮廓提前显示整片面板，不能从一个点向空处放射来冒充平面推进。
-玩家依照左右拍次序移动到门洞位置；通道中心只左右相差 2 格，给予中前期玩家充足余量。两侧符印代表发射顺序，面板生成区域均保持在 BOSS 一侧。</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>轨「左式」：t=20/60/100/140，18 发/拍，青。轨「右式」：t=40/80/120/160，18 发/拍，金。均场景一份，按主目标锁轴；各拍 18 个独立出生点、同方向 F。总计 144 发/轮。</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>面板有效列 x=−7.5/−5/−2.5/+2.5/+5/+7.5，再加左/右平移 −1/+1｜y=−2/0/+2｜弹径 0.40｜速度 0.25 格/tick=5 格/秒｜中央水平净宽 4.6 格｜寿命 120 tick｜倍率 1.0。</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>240 tick。8 拍、每 20 tick 一拍，从 20 至 160；同侧间隔 40 tick。t=0 锁轴，此轮所有门洞位置固定；220 收束。</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>t=0..160 锁位；161..239 游走。左右符印交替点亮，面板用无害细点提示门洞，预警与真实出生位置重合。</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>左青 #66E8FF；右金 #F2C14E；颜色与横移方向一一对应。</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>待实现：第 2 卡；lang ...yakumo_ran.2。原创残式，不再借前鬼后鬼之名宣称完整官方符卡。带门面板需要明确几何，不能以 CAGE(gap) 替代。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="260" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>共通底线 1/2（沿用旧稿，待复核）</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>坐标·预警·走位·多人</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Coordinates, Fairness, Movement, Multiplayer</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>【坐标】锁轴时记录 BOSS 眼位 O 与主目标胸口 T（脚位上移 0.9 格）；F=O→T，R=水平右，U=与 F、R 正交；近竖直时用上一有效 R。P(x,y,z)=O+xR+yU+zF，x/y/z 单位为格。锁定后的原点、轴、目标点都是世界快照，不随 BOSS 或玩家继续转动。
+【预警】所有威胁从 BOSS 附近可见的前方发射区进入；不在目标周围临时造环，不在身后生成近距离直瞄弹。每个发射组提前至少 20 tick 显示无伤符印；激光提前 30 tick 显示与实际光束一致的线。普通弹实际出生点距任何存活战斗玩家至少 6 格；计入碰撞体积后，预警开始至最早接触至少 1 秒。
+【取消】出生不满足条件的整个组本轮取消，符印淡出；不平移到玩家附近补发，不积压到下一拍。
+【走位】地面玩家也能从水平缺口通过；主通路净宽至少 2.5 格（按实际碰撞净宽，不把两颗弹中心距当净宽）。跳跃和飞行是额外解法，不作为唯一解。
+【多人】整张场景阵列只一份，共用主目标的轴；个人点名仅指定轨按目标复制，最多 5 人，均从 BOSS 一侧发出。目标列表在子轮锁轴时快照；目标死亡/退出后取消该目标余下个人拍，不转给其他人。每条主弹路必须覆盖快照目标附近战斗区，禁止只朝侧面放射。</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>旧稿共通契约；重设计时可复用，但需按新卡复核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="188" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>八云蓝残魂</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>3 阶段</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>(62.5%, 75%]</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>狐火「交差余焰」</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Foxfire: Crossing Embers</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>两条斜向推进的狐火弹带交错，中间两次白色短促点名。t=0 锁主轴，左右中心分别为 P(−5,0,0)、P(+5,0,0)。两侧各发 6 拍，左 t=20/40/60/80/100/120，右 t=30/50/70/90/110/130。每拍 9 发为 3×3 方阵，间距 2 格；左方向 normalize(F+0.22R)，右方向 normalize(F−0.22R)，全部方向沿主轴固定，形成缓慢靠近、交叉后分开的两条带。
-t=50/110 分别锁定个人胸口位置并亮白色符印；t=70/130 每名玩家收到 3 发平行白弹，横向间距 1.6 格、速度 6 格/秒。白弹源为当前 BOSS 眼位快照，左右弹带不因白弹瞄准改变方向。玩家先辨认交差处的间隙，再短促侧移避开白弹；不在门洞里持续扫射。</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>轨「交差狐火」：左/右各 6×9=54 发，同轨同色，场景一份；间隔 10 tick 交替，共108。轨「白符点名」：2×3=6 发/人，AIMED。单人总计114。普通弹不分裂、不追踪。</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>主阵 3×3 / 间距2 / 弹径0.40 / 0.25格每tick(5格每秒)｜左右倾角约12.4°｜点名3发 / 间距1.6 / 弹径0.35 / 0.30格每tick(6格每秒)｜提示均20tick｜寿命120tick｜倍率1.0。</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>240 tick。主阵20..130交替；点名预告50/110、发射70/130；最后一拍130，220收束。不得用 FAN.phaseStep 代替两条实际方向。</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>t=0..130锁位；131..239游走。左右符印持续可见，发射侧短闪；白色符印与青色主阵分开提示。</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>交差狐火青 #66E8FF；点名白 #F5F0E6。</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>待实现：第3卡；lang ...yakumo_ran.3。原创；交差结构不能直接解释为官方四面楚歌的完整摆动通道。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="260" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>共通底线 2/2（沿用旧稿，待复核）</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>预算·收束·移动锁</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Budget, Cleanup, Movement Lock</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>【预算】单拍实际展开实体数 ≤48（含子弹与后续派生），多轨错峰；审查真实出生数，不只看 count。普通弹默认无派生分裂、无隐形伤害；球弹撞方块消解，激光被方块裁剪。球弹直径默认 0.40 格，大玉仅终符用 0.70；激光半径 0.18 格（直径 0.36）。每发出生年龄 120 tick 后消解，特殊卡另列更短寿命。预警符印/虚线不碰撞、不伤害、不计弹数。
+【收束】每轮 t=220 停止本卡全部判伤，并在 10 tick 内淡出本卡残弹与预警；t=230..239 清空重整；t=240 循环边界重新锁轴。常规攻击结束后仍有在途弹，不能把“停止生成”写成无压力。血量跨下一阈值则挂起到边界切卡，先清旧卡；不得跨卡残弹叠加。死亡立即清理全部归属攻击。
+【移动锁】锁位只固定 BOSS 位置，不追随玩家高度；锁位结束恢复既有通用可达性游走。选点优先距主目标约 14~22 格，属于评分目标，不保证距离，也不直接以远离玩家为位移方向。符印锚定到本轮世界快照。</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>旧稿共通契约；重设计时可复用，但需按新卡复核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="220" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>八云蓝残魂</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>4 阶段</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>(50%, 62.5%]</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>残辉「狐狸妖怪激光」</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Remnant Radiance: Fox-Tanuki Laser</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>本卡是残魂唯一的激光招牌：一条可诱导的弹群轴，接上两对横向光束。每轮两组 b=0/100；b 时记录 O/T/F，b+20/28/36 从 O 各发 9 发3×3狐火群（间距1.5），以6格/秒沿F飞行，整组不重瞄。
-在 b+40 于轴上 Q1=O+6F、Q2=O+10F 显出两枚激光节点。每节点各有向+R与−R的水平射线；起点分别为 Q+1.5R 和 Q−1.5R、射线向外，故轴线周围保留3格中心断口。每条有效长度8格、半径0.18。b+40..69仅预警，b+70..89激活，b+90全部熄灭；4道光束同一时刻激活。第二组在第一组熄灭后才重新锁轴。
-解法为先把弹群引向旧站位，侧移让弹群通过，再观察节点和间隔。玩家可从中心断口、两节点之间、射线外端或高度差绕过。光束沿发射轴布置，不在玩家身边造星，不旋转、不追踪、不向背后补刀。</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>轨「引线狐火」：每组3×9=27发，场景一份，按主目标诱导。轨「残辉」：每组4道，分为两节点×左右各1道。2组总计54普通弹+8道激光；不会按人数复制整套光阵。</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>普通弹直径0.40 / 6格每秒 / 寿命70tick（须在本组光束激活前后及时退场）｜节点6/10格｜激光半径0.18、长8格、预警30tick(1.5s)、激活20tick(1s)、中心物理净宽约2.64格｜普通弹与激光倍率1.0。每组真实射线激活前必须重新验证通路。</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>240tick。第一组预告0、球弹20/28/36、激光预告40、激活70..89；第二组100/120/128/136/140/170..189；190后无新攻击，220收束。两组激光不重叠。</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>t=0..189锁位；190..239游走。球弹提示青，节点提示黄；光束未激活时细虚线，激活时清晰实线，关闭立刻停止判伤。</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>引线青 #66E8FF；激光黄 #FFE066。</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>待实现：第4卡；lang ...yakumo_ran.4。官方“弹群轨迹衍生横向激光”的局部改编；需组级轴快照、共享轴节点和真实断口，不能用 AROUND_TARGET 代替。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="260" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>考据与命名说明</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>资料截至 2026-10-25</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>官方卡名、译名与取舍</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Sources and Naming</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>主战卡池以《东方妖妖梦》Extra（10 张）与 Phantasm 中 BOSS（2 张）为准。中文名为项目内常用译名，英文名取 Touhou Wiki 译名，不标作官方英文。
+Extra 顺序：仙狐思念 → 十二神将之宴 → 狐狸妖怪激光 → 四面楚歌 Charming → 天狐公主 -Illusion- → Ultimate Buddhist → 片面接触 → 式神「橙」→ 狐狗狸先生的契约 → 饭纲权现降临。Phantasm 中 BOSS：前鬼后鬼的守护 → 凭依荼吉尼天。
+旧稿把「式神大星」当作来源不明/非官方卡，实际是《秘封噩梦日记》噩梦周三弹幕梦4 与灵乌路空的合作卡，官方存在；但它不是妖妖梦主战卡。旧稿还漏掉天狐公主、Ultimate Buddhist、式神橙、狐狗狸契约、凭依荼吉尼天；重设计需明确是“补齐”还是“有意舍弃”。
+官方卡没有血量分段；表中 C 列统一 —，8 阶段的血量区间由重设计决定。正式本地化仍称「八云蓝残影」；本页按本次需求称「残魂」，不表示已修改实体名称。
+来源：Touhou Wiki「Ran Yakumo/Spell Cards」；萌娘百科「八云蓝/符卡信息」；THBWiki 符卡列表；hossy.info「妖妖梦 Extra 解体新书 4/5」逐卡攻略。</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="124" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>八云蓝残魂</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>5 阶段</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>(37.5%, 50%]</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>残式「留影之符」</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Remnant Formula: Lingering Sigils</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>教玩家读同一片弹幕的启停。两组 b=0/90，各自锁定主轴并显示带门面板。b+20/32/44 分三拍生成面板，每拍18发，列为−7.5/−5/−2.5/+2.5/+5/+7.5、行为−2/0/+2，沿F整体推进。第一组门中心x=−1，第二组x=+1，平移施加到所有出生点。
-每片从出生年龄a=0开始以4格/秒飞行，a=0..20线性减速到0，总前进2格；a=20..40停留1秒；a=40..60线性加速到6格/秒，再匀速向原F方向飞出。停留时仍可碰撞受伤，不能把“静止”当无害。a=30时所有弹统一闪亮一次并提示音，预告0.5秒后开始恢复推进；恢复时不重新瞄准，也不发射中心追踪弹。
-玩家在可见停顿期间选好横向门洞，穿过后不必追着BOSS走。三片同门排列形成纵深，而不是三套不同方向堵路。</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>轨「留影面板」×1：2组×3拍×18=108发，场景一份。位置=出生点+F×分段速度积分；无转向、无自旋、无回收、无派生。</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>面板18发/拍｜列距2.5、行距2、中央净宽4.6｜弹径0.40｜速度曲线(tick,格/tick)：(0,0.20)→(20,0)→(40,0)→(60,0.30)，此后0.30｜寿命120tick｜提示20tick｜倍率1.0。</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>240tick。第一组预告0、发射20/32/44；第二组预告90、发射110/122/134；最后一片恢复推进174；220全卡停止判伤，不将残留悬停弹留到下一卡。</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>t=0..134锁位；135..239游走，已发弹不跟随。停留阶段弹体维持可见与碰撞，起动闪光只是提示、不改变判定尺寸。</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>白 #F5F0E6；停顿时提高亮度，不突然换为其他轨身份色。</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>待实现：第5卡；lang ...yakumo_ran.5。原创残式，仅复用减速—停留—再推进，不冒充片面接触的完整旋转回收。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="260" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>八云蓝残魂</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>6 阶段</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>(25%, 37.5%]</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>残式「双使回转」</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Remnant Formula: Turning Servants</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>只做一次可见转向，不做完整回收。t=0锁主轴；左源P(−4,0,0)、右源P(+4,0,0)。左在20/44/68/92发射，右在32/56/80/104接上；每拍12发排成4列×3行，列间距1.5、行间距2，整片同速同方向。左片初始方向相对F水平向右偏25°，右片向左偏25°，先以4格/秒直飞30tick。
-出生年龄a=20亮起弧线方向提示；a=30..60保持4格/秒并匀速转向，将偏角从±25°变到0°（总计25°、持续1.5秒），之后沿F以4格/秒直飞。每颗弹使用同一片的平移路径，保持原始相对偏移，不因各自半径而聚到一点。蓝/金两片只是镜像转向，不绕玩家盘旋，不再折返。
-玩家在转向前观察弹片向内靠拢的趋势，从外侧或中央较宽区域通过；转向完成后不会突然再次瞄准。</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>轨「左使」：4×12=48发、青。轨「右使」：4×12=48发、金。场景一份，共96发。每片4×3阵列在垂直初始方向的平面内，所有弹共享轨迹增量；无编队径向收缩。</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>每拍12发｜4列横坐标−2.25/−0.75/+0.75/+2.25；3行−2/0/+2｜弹径0.40｜恒速0.20格/tick=4格/秒｜直飞30tick→匀转30tick→直飞｜偏角±25°→0｜寿命120tick｜倍率1.0。弧线实际位置由速度方向积分求解；严禁靠瞬间改方向制造折角。</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>240tick。发射20..104，每12tick交替；最晚转向结束164；220收束。每拍提前20tick符印提示；转向前另有10tick弧线提示。</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>t=0..104锁位；105..239游走。提示弧线只显示未来转向方向，绝不带伤害。已发弹沿自己的锁定轴运动。</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>左青 #66E8FF；右金 #F2C14E；颜色固定对应弯向。</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>待实现：第6卡；lang ...yakumo_ran.6。分段平滑方向运动需先核对引擎表达能力；不要用两条重叠 FAN 加 phaseStep 假装回转。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="260" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>八云蓝残魂</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>7 阶段</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>(12.5%, 25%]</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>残式「双使合奏」</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Remnant Formula: Duet of Servants</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>组合已学规则，不再增加新运动。t=0锁主轴；沿用卡2的左右交替带门面板：左20/60/100/140，右40/80/120/160，每拍18发，门中心交替−1/+1。全部面板改用卡5同一条减速—停留—再推进曲线，因此玩家先看到停留的门洞，再随面板启动穿过。
-白色点名只两次：t=40/100记录每名玩家胸口；t=60/120从当时已记录的BOSS源点各发3枚平行白弹，横向间距1.6格，以5格/秒朝旧站位推进。点名不持续刷新，不瞄准玩家未来的门洞。白弹最长存活70tick，减少后段与多片启动重叠。
-玩家按颜色和左右顺序读门，在启停之间小幅侧移解开点名。两个机制形成短时叠加，而不是再叠加激光、弧弹或独立底噪。多张面板联合碰撞必须仍有至少2.5格的可达水平通路。</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>轨「双使留影」：8×18=144发，场景一份；单轨各拍左/右符印交替，弹体统一青色，门位置由符印位置提示。轨「白符点名」：2×3=6发/人、白。单人150发/轮。</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>主阵沿用卡2几何、卡5速度曲线与120tick寿命｜点名3发、间距1.6、直径0.35、速度0.25格/tick=5格/秒、寿命70tick｜两轨倍率1.0｜每拍主阵18，点名按人3；同tick单人最多21发。</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>240tick。面板20..160每20tick；白弹锁40/100、发60/120；最后主片a=40即t=200恢复推进，220收束，给末片20tick推进表现。循环边界统一清旧卡。</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>t=0..160锁位；161..239游走。起动前0.5秒闪亮；白点名用独立白符印和较轻提示音，避免与整片启停提示混淆。</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>主阵青 #66E8FF；白符 #F5F0E6；符印左右位置辅助读门。</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>待实现：第7卡；lang ...yakumo_ran.7。替换来源未核实的“地妖符·式神大星”；不是官方卡名。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="260" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>八云蓝残魂</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>8 阶段</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>[0%, 12.5%]</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>魂辉「九尾余光」</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Soul Radiance: Nine-Tailed Afterglow</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>残魂终符只把狐火与双使两种能力合奏到最高强度。每轮三段，每段起点b=0/60/120，重新记录目标快照。主轨每段b+20/28/36/44发射9发3×3狐火群，规则与卡1一致，每名目标一份；从第一段到第三段，主轨速度依次5/5.5/6格每秒，拍数和瞄准方式不变。
-第一段只有狐火；第二段加入双使交差：b+24左源、b+40右源各发12发4×3方阵；第三段在b+24/40发左源、b+32/48发右源，共4片。双使几何采用卡6的4×3排布，源点P(±5,0,0)，但方向固定为 normalize(F±0.22R)，速度4格每秒，全程直飞，不转弯。副轨仅场景一份，按每段主目标轴锁定。
-三段依次为单轨36发、双轨60发、双轨84发（单人），形成明显层次；每轮重新从单轨开始，避免无上限堆压。t=168最后一片副轨后只处理在途弹，220收束。尾部九道无害狐火余辉合拢并熄灭，表示魂力耗尽一次，再进入下一轮。终符不加入新机关，不借饭纲权现降临之名。</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>轨「九尾狐念」：3段×4拍×9=108发/人，AIMED。轨「双使余光」：第二段2×12、第三段4×12=72发，全场一份。单人180发/轮；5人名义612发/轮（含公共72），需按近邻玩家交叉弹路另验。九道尾光只是演出，不计实体弹。</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>主轨直径0.40、间距1.5、速度0.25/0.275/0.30格每tick；副轨直径0.40、4×3/横距1.5纵距2、速度0.20格每tick｜预警20tick｜寿命120tick｜两轨倍率1.1，不叠原实现1.4倍｜单拍≤12发/目标或公共。</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>240tick。主轨20/28/36/44、80/88/96/104、140/148/156/164；副轨84/100、144/152/160/168。0/60/120分别锁定新段，新增副轨在60/120已有符印预告；220收束，240从第一段重新开始。</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>t=0..168锁位；169..239游走。三段以一枚、两枚、两枚更亮符印递进；不能用屏幕遮挡性全屏闪光制造终局感。重整尾光无碰撞。</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>主狐火金 #F2C14E；副轨紫 #9C6BFF，较慢且方阵更宽；不与白色点名语义混用。</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>待实现：第8卡；lang ...yakumo_ran.8。原创残魂终符；完整幻神“饭纲权现降临”及多弹种层叠体系保留给正主。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="300" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>八云蓝残魂</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>实现前核对 / 验收</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>全部八卡</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>规则表为目标，不代表现有引擎已支持</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Implementation and Acceptance Notes</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>先落实共通锁轴与清弹，再逐卡实现；主战斗设计不能建立在现有注释的假语义上。已静态发现：AROUND_TARGET当前缺完整环周分量、出生点可离目标很近；CAGE未实际读取gap；FAN未读取phase，双轨可能完全重叠；RING_FACING只有面内径向速度，不会自行向玩家推进。本表不依赖这些错误行为。
-每卡以生存模式在平地、起伏地、近身、14/22格距离及1/2/5人场检查：预警与真实命中一致；近身取消整组而不补刀；地面玩家有可达横向通路；主弹幕确实进入玩家附近；移动不会拖拽已发队形；跨血线在边界切换、无旧弹伤害；卡4前后两组激光不重叠；卡5/7静止弹碰撞正常；卡6无瞬间折角；卡8分段重新锁轴且每轮强度重置。
-先按实际命中与位置验证有效密度，再调发射间隔；不可用加伤害代替补齐表演。多人时既审实体预算，也审不同玩家的个人弹路交叉是否堵死公共通路。若实测需修改规则，回写本表而不是让注释与实现分叉。</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>检查每条轨1周期及多周期累计发射数、实际展开数、寿命与循环清理。显式绝对拍写入12秒循环，不依赖repeatEvery处理偏移子拍。位置快照与共享方向属于编排能力，不造承载编队状态的实体。</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>单人名义总数（普通弹 / 激光）：1=108/0；2=144/0；3=114/0；4=54/8；5=108/0；6=96/0；7=150/0；8=180/0。每轮平均数不等于瞬时存活数；把出生无害/静止/在途/淡出分别核算。</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>所有卡12秒；t=220停止伤害，t=230完成淡出，t=240下一轮。需要计时轮次状态与归属清理；现有循环只解决发射重放，不能视作已完成收束功能。</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>基础HP、伤害、战斗时长仍待实测。现有血量选择可能在边界跳过中间阈值；八张表不是八卡必定完整演出的保证，若要逐卡必演需另确认阶段推进规则。</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>视觉差异至少在颜色/尺寸/速度/形状中一项可辨；预警不得与有伤害弹使用完全相同显示。</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>候选落点：BossCards、TrackRunner/Track、Geometry、DanmakuEmitter、YakumoRanEntity；分段运动、预警与清理按现有基础设施复用，缺项先明确再实现。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="300" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>八云蓝残魂</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>考据与命名说明</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>资料截至 2026-10-12</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>残式改编与原创必须区分</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Sources and Naming</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>官方内容核对以《东方妖妖梦》Extra为主，资料为原作攻略记录而非官方开发说明。仙狐思念的重点是节奏自机狙；狐狸妖怪激光是弹群轨迹衍生横向光束；十二神将为十二魔法阵协作；四面楚歌为摆动细弹通道与交叉大玉；片面接触为减速停止、旋转收束与再展开；饭纲权现为逐层增加弹种。
-本页只有卡1、卡4明确借用官方名称并加残式/残辉前缀；其余六卡为本项目拟定原创残式。卡6只有一次转向，不等于原作片面接触。此前“式神大星”未核实官方出处，不作为考据依据。前鬼后鬼的守护虽为官方卡，但出自Phantasm道中蓝，不是Extra主战顺序。</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>来源1：https://hossy.info/game/toho/y_extra4.php（Extra前五卡）
-来源2：https://hossy.info/game/toho/y_extra5.php（Extra后五卡）
-来源3：https://wikiwiki.jp/thk/妖/EX（逐卡攻略，检索交叉核对）
-来源4：https://zh.moegirl.org.cn/八云蓝/符卡信息（符卡目录、名称与使用场合）</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>本表所有发数、时间、格数、倍率都是三维残魂改编初值，不是原作数值。英文卡名是拟定翻译，不标作官方英文。</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>后续实机调平衡需同步更新本页；版本状态由“设计稿”变更为“已实现/已验证”时须对应实际检查。</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>保留正主成长空间；本页不新增瞬移、召唤实体、移动牢笼或大型旋转光阵。</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>沿用角色金/青/白/黄/紫色盘；不依靠完整九尾神格演出表现残魂强度。</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>调查参照：BossCards.java:474起、Geometry.java、TrackRunner.java、YakumoRanEntity.java、GensokyouConfig.java:1032起；行号为本次调查时位置。</t>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>现行代码对照</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>旧实现与官方卡池的差异</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Current Code vs Official Pool</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>现行 YakumoRanPrograms 八卡：1 仙狐思念、2 前鬼后鬼的守护、3 狐狸妖怪激光、4 四面楚歌、5 十二神将之宴、6 片面接触、7 式神大星、8 饭纲权现降临。
+官方妖妖梦 Extra 未实现：天狐公主 -Illusion-、Ultimate Buddhist、式神「橙」、狐狗狸先生的契约；Phantasm 未实现：凭依荼吉尼天。第 7 卡用的是《秘封噩梦日记》合作卡。
+现行 BossCards#yakumoRan、YakumoRanPrograms 与 lang 键 1–8 是上一版占位/旧稿，重设计后应整体替换，不保留旧轨道。</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>参考：src/main/java/com/bitsson/gensokyou/danmaku/program/content/YakumoRanPrograms.java；BossCards.java；lang/zh_cn.json。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L14"/>
-  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
